--- a/results/qwen3_5_9b/comparison_SimpleRAG/SimpleRAG_costs.xlsx
+++ b/results/qwen3_5_9b/comparison_SimpleRAG/SimpleRAG_costs.xlsx
@@ -472,13 +472,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76.47203207015991</v>
+        <v>160.1122732162476</v>
       </c>
       <c r="B2" t="n">
-        <v>1434.66015625</v>
+        <v>1439.83984375</v>
       </c>
       <c r="C2" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -487,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8389444351196289</v>
+        <v>1.101526260375977</v>
       </c>
       <c r="G2" t="n">
-        <v>75.63308262825012</v>
+        <v>159.0107429027557</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -498,13 +498,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.984262704849243</v>
+        <v>365.7186002731323</v>
       </c>
       <c r="B3" t="n">
-        <v>1434.87109375</v>
+        <v>1440.5390625</v>
       </c>
       <c r="C3" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.319493293762207</v>
+        <v>1.400856733322144</v>
       </c>
       <c r="G3" t="n">
-        <v>1.664765357971191</v>
+        <v>364.3177394866943</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -524,13 +524,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.137856483459473</v>
+        <v>12.39716982841492</v>
       </c>
       <c r="B4" t="n">
-        <v>1435.0078125</v>
+        <v>1440.578125</v>
       </c>
       <c r="C4" t="n">
-        <v>14.1</v>
+        <v>12.2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05013179779052734</v>
+        <v>1.236253499984741</v>
       </c>
       <c r="G4" t="n">
-        <v>1.087722063064575</v>
+        <v>11.16091394424438</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.754924535751343</v>
+        <v>10.72837734222412</v>
       </c>
       <c r="B5" t="n">
-        <v>1435.07421875</v>
+        <v>1441.78125</v>
       </c>
       <c r="C5" t="n">
-        <v>9.1</v>
+        <v>12.1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -565,10 +565,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05014634132385254</v>
+        <v>0.3296880722045898</v>
       </c>
       <c r="G5" t="n">
-        <v>1.704776048660278</v>
+        <v>10.398686170578</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -576,13 +576,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.332970142364502</v>
+        <v>13.05308818817139</v>
       </c>
       <c r="B6" t="n">
-        <v>1435.16015625</v>
+        <v>1441.79296875</v>
       </c>
       <c r="C6" t="n">
-        <v>8.9</v>
+        <v>14.2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -591,10 +591,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0514833927154541</v>
+        <v>0.2729661464691162</v>
       </c>
       <c r="G6" t="n">
-        <v>1.28148365020752</v>
+        <v>12.78011965751648</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -602,13 +602,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.759987354278564</v>
+        <v>13.98302745819092</v>
       </c>
       <c r="B7" t="n">
-        <v>1435.3125</v>
+        <v>1441.94140625</v>
       </c>
       <c r="C7" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -617,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08331394195556641</v>
+        <v>0.2783322334289551</v>
       </c>
       <c r="G7" t="n">
-        <v>1.676670551300049</v>
+        <v>13.70469331741333</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -628,13 +628,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.224164962768555</v>
+        <v>28.58141660690308</v>
       </c>
       <c r="B8" t="n">
-        <v>1435.36328125</v>
+        <v>1442.04296875</v>
       </c>
       <c r="C8" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04852032661437988</v>
+        <v>0.237790584564209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.175642251968384</v>
+        <v>28.34362387657166</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4575881958007812</v>
+        <v>12.63077235221863</v>
       </c>
       <c r="B9" t="n">
-        <v>1435.36328125</v>
+        <v>1442.16015625</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>14.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08756685256958008</v>
+        <v>0.2958860397338867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3700182437896729</v>
+        <v>12.33488368988037</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4116129875183105</v>
+        <v>26.68319201469421</v>
       </c>
       <c r="B10" t="n">
-        <v>1435.44140625</v>
+        <v>1442.22265625</v>
       </c>
       <c r="C10" t="n">
-        <v>8.9</v>
+        <v>14.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -695,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04895162582397461</v>
+        <v>0.247819185256958</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3626582622528076</v>
+        <v>26.43537044525146</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -706,13 +706,13 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.5006237030029297</v>
+        <v>19.38218235969543</v>
       </c>
       <c r="B11" t="n">
-        <v>1435.4453125</v>
+        <v>1442.26953125</v>
       </c>
       <c r="C11" t="n">
-        <v>10.4</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04920029640197754</v>
+        <v>0.2743501663208008</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4514205455780029</v>
+        <v>19.10783004760742</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -732,13 +732,13 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.275068283081055</v>
+        <v>11.34494733810425</v>
       </c>
       <c r="B12" t="n">
-        <v>1435.484375</v>
+        <v>1442.31640625</v>
       </c>
       <c r="C12" t="n">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08544230461120605</v>
+        <v>0.2448604106903076</v>
       </c>
       <c r="G12" t="n">
-        <v>2.189622640609741</v>
+        <v>11.10008430480957</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.4389102458953857</v>
+        <v>16.30511331558228</v>
       </c>
       <c r="B13" t="n">
-        <v>1435.59765625</v>
+        <v>1442.33984375</v>
       </c>
       <c r="C13" t="n">
-        <v>17.1</v>
+        <v>15.5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04858088493347168</v>
+        <v>0.245225191116333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3903264999389648</v>
+        <v>16.05988502502441</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -784,13 +784,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.324690341949463</v>
+        <v>20.72277021408081</v>
       </c>
       <c r="B14" t="n">
-        <v>1435.640625</v>
+        <v>1442.33984375</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>12.7</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04912018775939941</v>
+        <v>0.2696521282196045</v>
       </c>
       <c r="G14" t="n">
-        <v>1.275567293167114</v>
+        <v>20.45311570167542</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -810,13 +810,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.671306848526001</v>
+        <v>11.35493922233582</v>
       </c>
       <c r="B15" t="n">
-        <v>1435.6953125</v>
+        <v>1442.37109375</v>
       </c>
       <c r="C15" t="n">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04772257804870605</v>
+        <v>0.3284964561462402</v>
       </c>
       <c r="G15" t="n">
-        <v>1.623580455780029</v>
+        <v>11.02643966674805</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.5107827186584473</v>
+        <v>27.76741623878479</v>
       </c>
       <c r="B16" t="n">
-        <v>1435.7578125</v>
+        <v>1442.40234375</v>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -851,10 +851,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05155420303344727</v>
+        <v>0.241471529006958</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4592256546020508</v>
+        <v>27.52594113349915</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,13 +862,13 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.133055925369263</v>
+        <v>16.28290700912476</v>
       </c>
       <c r="B17" t="n">
-        <v>1435.796875</v>
+        <v>1442.5703125</v>
       </c>
       <c r="C17" t="n">
-        <v>9.4</v>
+        <v>13.8</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05006504058837891</v>
+        <v>0.237107515335083</v>
       </c>
       <c r="G17" t="n">
-        <v>1.082988739013672</v>
+        <v>16.04579734802246</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.8764533996582031</v>
+        <v>21.1650698184967</v>
       </c>
       <c r="B18" t="n">
-        <v>1435.796875</v>
+        <v>1442.6796875</v>
       </c>
       <c r="C18" t="n">
-        <v>8.800000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0492098331451416</v>
+        <v>0.2524657249450684</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8272414207458496</v>
+        <v>20.91260123252869</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.398208856582642</v>
+        <v>13.7309775352478</v>
       </c>
       <c r="B19" t="n">
-        <v>1435.796875</v>
+        <v>1442.765625</v>
       </c>
       <c r="C19" t="n">
-        <v>8.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -929,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09425926208496094</v>
+        <v>0.2454080581665039</v>
       </c>
       <c r="G19" t="n">
-        <v>1.303947448730469</v>
+        <v>13.48556685447693</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -940,13 +940,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6292998790740967</v>
+        <v>27.69061994552612</v>
       </c>
       <c r="B20" t="n">
-        <v>1435.80078125</v>
+        <v>1442.86328125</v>
       </c>
       <c r="C20" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04818296432495117</v>
+        <v>0.2386364936828613</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5811145305633545</v>
+        <v>27.45198035240173</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.240517139434814</v>
+        <v>14.50324845314026</v>
       </c>
       <c r="B21" t="n">
-        <v>1436.0703125</v>
+        <v>1442.87109375</v>
       </c>
       <c r="C21" t="n">
-        <v>8.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1213269233703613</v>
+        <v>0.2455160617828369</v>
       </c>
       <c r="G21" t="n">
-        <v>1.119187593460083</v>
+        <v>14.25773024559021</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -992,13 +992,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1.365905046463013</v>
+        <v>15.0450713634491</v>
       </c>
       <c r="B22" t="n">
-        <v>1436.12109375</v>
+        <v>1442.87890625</v>
       </c>
       <c r="C22" t="n">
-        <v>8.9</v>
+        <v>13.9</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04926228523254395</v>
+        <v>0.2446608543395996</v>
       </c>
       <c r="G22" t="n">
-        <v>1.316640138626099</v>
+        <v>14.80040574073792</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4961609840393066</v>
+        <v>36.80736088752747</v>
       </c>
       <c r="B23" t="n">
-        <v>1436.12890625</v>
+        <v>1442.890625</v>
       </c>
       <c r="C23" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04829525947570801</v>
+        <v>0.2396152019500732</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4478635787963867</v>
+        <v>36.56774258613586</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.187919616699219</v>
+        <v>14.4644033908844</v>
       </c>
       <c r="B24" t="n">
-        <v>1436.1328125</v>
+        <v>1442.90234375</v>
       </c>
       <c r="C24" t="n">
-        <v>9.1</v>
+        <v>13.9</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05022549629211426</v>
+        <v>0.2395079135894775</v>
       </c>
       <c r="G24" t="n">
-        <v>1.137691020965576</v>
+        <v>14.22489333152771</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1070,13 +1070,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4501781463623047</v>
+        <v>9.979879856109619</v>
       </c>
       <c r="B25" t="n">
-        <v>1436.1328125</v>
+        <v>1442.90625</v>
       </c>
       <c r="C25" t="n">
-        <v>12.2</v>
+        <v>14.9</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0893702507019043</v>
+        <v>0.2454454898834229</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3608052730560303</v>
+        <v>9.734431982040405</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.510486841201782</v>
+        <v>8.834078311920166</v>
       </c>
       <c r="B26" t="n">
-        <v>1436.19921875</v>
+        <v>1442.9921875</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2</v>
+        <v>12.4</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04884696006774902</v>
+        <v>0.2767970561981201</v>
       </c>
       <c r="G26" t="n">
-        <v>1.461637735366821</v>
+        <v>8.557279109954834</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1.326744079589844</v>
+        <v>10.23827743530273</v>
       </c>
       <c r="B27" t="n">
-        <v>1436.20703125</v>
+        <v>1443.12109375</v>
       </c>
       <c r="C27" t="n">
-        <v>18.4</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04909896850585938</v>
+        <v>0.2445876598358154</v>
       </c>
       <c r="G27" t="n">
-        <v>1.277642488479614</v>
+        <v>9.993687391281128</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1148,13 +1148,13 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2.467652797698975</v>
+        <v>6.928074359893799</v>
       </c>
       <c r="B28" t="n">
-        <v>1436.2109375</v>
+        <v>1443.16015625</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05246353149414062</v>
+        <v>0.2437715530395508</v>
       </c>
       <c r="G28" t="n">
-        <v>2.415187120437622</v>
+        <v>6.684297561645508</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5193507671356201</v>
+        <v>8.439210891723633</v>
       </c>
       <c r="B29" t="n">
-        <v>1436.2109375</v>
+        <v>1443.2265625</v>
       </c>
       <c r="C29" t="n">
-        <v>9.1</v>
+        <v>12.5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04853558540344238</v>
+        <v>0.2376666069030762</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4708130359649658</v>
+        <v>8.201541900634766</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1200,13 +1200,13 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.4102785587310791</v>
+        <v>13.08601450920105</v>
       </c>
       <c r="B30" t="n">
-        <v>1436.2109375</v>
+        <v>1443.3125</v>
       </c>
       <c r="C30" t="n">
-        <v>8.1</v>
+        <v>14.4</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04793906211853027</v>
+        <v>0.2410788536071777</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3623368740081787</v>
+        <v>12.8449330329895</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.4380490779876709</v>
+        <v>12.59663462638855</v>
       </c>
       <c r="B31" t="n">
-        <v>1436.2109375</v>
+        <v>1443.32421875</v>
       </c>
       <c r="C31" t="n">
-        <v>8.5</v>
+        <v>14.2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04803729057312012</v>
+        <v>0.2400929927825928</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3899977207183838</v>
+        <v>12.35653877258301</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1252,13 +1252,13 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.381005048751831</v>
+        <v>14.94927358627319</v>
       </c>
       <c r="B32" t="n">
-        <v>1436.2109375</v>
+        <v>1443.32421875</v>
       </c>
       <c r="C32" t="n">
-        <v>9.300000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04758119583129883</v>
+        <v>0.2361922264099121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.333421230316162</v>
+        <v>14.71307873725891</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.106777667999268</v>
+        <v>17.28743410110474</v>
       </c>
       <c r="B33" t="n">
-        <v>1436.296875</v>
+        <v>1443.33984375</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05308246612548828</v>
+        <v>0.2429637908935547</v>
       </c>
       <c r="G33" t="n">
-        <v>2.053693056106567</v>
+        <v>17.04446792602539</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1304,13 +1304,13 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.582678318023682</v>
+        <v>17.31186532974243</v>
       </c>
       <c r="B34" t="n">
-        <v>1436.31640625</v>
+        <v>1443.3515625</v>
       </c>
       <c r="C34" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04851651191711426</v>
+        <v>0.2443737983703613</v>
       </c>
       <c r="G34" t="n">
-        <v>1.534159183502197</v>
+        <v>17.06748843193054</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1330,13 +1330,13 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2.130998134613037</v>
+        <v>18.00968790054321</v>
       </c>
       <c r="B35" t="n">
-        <v>1436.421875</v>
+        <v>1443.3515625</v>
       </c>
       <c r="C35" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04872703552246094</v>
+        <v>0.2391109466552734</v>
       </c>
       <c r="G35" t="n">
-        <v>2.082268238067627</v>
+        <v>17.77057456970215</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2.697059631347656</v>
+        <v>14.74432563781738</v>
       </c>
       <c r="B36" t="n">
-        <v>1436.53515625</v>
+        <v>1443.4453125</v>
       </c>
       <c r="C36" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05309915542602539</v>
+        <v>0.2454111576080322</v>
       </c>
       <c r="G36" t="n">
-        <v>2.643957614898682</v>
+        <v>14.49891138076782</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1382,13 +1382,13 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.525054931640625</v>
+        <v>18.94883227348328</v>
       </c>
       <c r="B37" t="n">
-        <v>1436.5546875</v>
+        <v>1443.4453125</v>
       </c>
       <c r="C37" t="n">
-        <v>9.800000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05364584922790527</v>
+        <v>0.281712532043457</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4714062213897705</v>
+        <v>18.66711640357971</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.2687962055206299</v>
+        <v>17.63683772087097</v>
       </c>
       <c r="B38" t="n">
-        <v>1436.5546875</v>
+        <v>1443.56640625</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>14.1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.06898164749145508</v>
+        <v>0.2465879917144775</v>
       </c>
       <c r="G38" t="n">
-        <v>0.199812650680542</v>
+        <v>17.3902473449707</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.4204061031341553</v>
+        <v>14.06314754486084</v>
       </c>
       <c r="B39" t="n">
-        <v>1436.5625</v>
+        <v>1443.6015625</v>
       </c>
       <c r="C39" t="n">
-        <v>8.5</v>
+        <v>14.3</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1449,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05163478851318359</v>
+        <v>0.2527048587799072</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3687689304351807</v>
+        <v>13.81043791770935</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.101215362548828</v>
+        <v>10.23899173736572</v>
       </c>
       <c r="B40" t="n">
-        <v>1436.5625</v>
+        <v>1443.63671875</v>
       </c>
       <c r="C40" t="n">
-        <v>8.9</v>
+        <v>13.1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04960846900939941</v>
+        <v>0.2441120147705078</v>
       </c>
       <c r="G40" t="n">
-        <v>1.051604509353638</v>
+        <v>9.994876861572266</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.4448699951171875</v>
+        <v>13.77950930595398</v>
       </c>
       <c r="B41" t="n">
-        <v>1436.5625</v>
+        <v>1443.64453125</v>
       </c>
       <c r="C41" t="n">
-        <v>9.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05235671997070312</v>
+        <v>0.239856481552124</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3925108909606934</v>
+        <v>13.53964972496033</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1.408112525939941</v>
+        <v>8.499035835266113</v>
       </c>
       <c r="B42" t="n">
-        <v>1436.5625</v>
+        <v>1443.64453125</v>
       </c>
       <c r="C42" t="n">
-        <v>8.9</v>
+        <v>11.9</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04854369163513184</v>
+        <v>0.2434766292572021</v>
       </c>
       <c r="G42" t="n">
-        <v>1.359566211700439</v>
+        <v>8.255556344985962</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1538,13 +1538,13 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1.95990252494812</v>
+        <v>12.3998806476593</v>
       </c>
       <c r="B43" t="n">
-        <v>1436.5703125</v>
+        <v>1443.64453125</v>
       </c>
       <c r="C43" t="n">
-        <v>9.300000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.04887628555297852</v>
+        <v>0.2498202323913574</v>
       </c>
       <c r="G43" t="n">
-        <v>1.911023616790771</v>
+        <v>12.15005803108215</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.3958652019500732</v>
+        <v>9.906358003616333</v>
       </c>
       <c r="B44" t="n">
-        <v>1436.66796875</v>
+        <v>1443.64453125</v>
       </c>
       <c r="C44" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.04761886596679688</v>
+        <v>0.2687423229217529</v>
       </c>
       <c r="G44" t="n">
-        <v>0.348236083984375</v>
+        <v>9.637613296508789</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1.395802974700928</v>
+        <v>11.77480959892273</v>
       </c>
       <c r="B45" t="n">
-        <v>1436.84765625</v>
+        <v>1443.734375</v>
       </c>
       <c r="C45" t="n">
-        <v>9.199999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.04942727088928223</v>
+        <v>0.2444148063659668</v>
       </c>
       <c r="G45" t="n">
-        <v>1.346372842788696</v>
+        <v>11.53039193153381</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1.423894643783569</v>
+        <v>19.91411447525024</v>
       </c>
       <c r="B46" t="n">
-        <v>1436.890625</v>
+        <v>1443.78125</v>
       </c>
       <c r="C46" t="n">
-        <v>10.5</v>
+        <v>15.1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.04790472984313965</v>
+        <v>0.285128116607666</v>
       </c>
       <c r="G46" t="n">
-        <v>1.375987529754639</v>
+        <v>19.62898397445679</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.937818765640259</v>
+        <v>19.87475156784058</v>
       </c>
       <c r="B47" t="n">
-        <v>1436.8984375</v>
+        <v>1443.91796875</v>
       </c>
       <c r="C47" t="n">
-        <v>18.1</v>
+        <v>12.7</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04979729652404785</v>
+        <v>0.2409555912017822</v>
       </c>
       <c r="G47" t="n">
-        <v>1.888018846511841</v>
+        <v>19.63379287719727</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.261324405670166</v>
+        <v>18.18504762649536</v>
       </c>
       <c r="B48" t="n">
-        <v>1436.90234375</v>
+        <v>1443.99609375</v>
       </c>
       <c r="C48" t="n">
-        <v>18</v>
+        <v>15.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04862666130065918</v>
+        <v>0.2447407245635986</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2126944065093994</v>
+        <v>17.94030427932739</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2.098782300949097</v>
+        <v>17.59465980529785</v>
       </c>
       <c r="B49" t="n">
-        <v>1436.9140625</v>
+        <v>1444.0234375</v>
       </c>
       <c r="C49" t="n">
-        <v>11.5</v>
+        <v>13.9</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1709,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04910969734191895</v>
+        <v>0.2433815002441406</v>
       </c>
       <c r="G49" t="n">
-        <v>2.049670219421387</v>
+        <v>17.3512761592865</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.033989906311035</v>
+        <v>19.64222168922424</v>
       </c>
       <c r="B50" t="n">
-        <v>1436.9140625</v>
+        <v>1444.078125</v>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>13.9</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.04962921142578125</v>
+        <v>0.2394795417785645</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9843583106994629</v>
+        <v>19.40273952484131</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1746,13 +1746,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.111335754394531</v>
+        <v>21.14945268630981</v>
       </c>
       <c r="B51" t="n">
-        <v>1436.91796875</v>
+        <v>1444.1015625</v>
       </c>
       <c r="C51" t="n">
-        <v>9.199999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.04832911491394043</v>
+        <v>0.2385873794555664</v>
       </c>
       <c r="G51" t="n">
-        <v>1.063004016876221</v>
+        <v>20.91086292266846</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.403618097305298</v>
+        <v>12.17007875442505</v>
       </c>
       <c r="B52" t="n">
-        <v>1436.921875</v>
+        <v>1444.109375</v>
       </c>
       <c r="C52" t="n">
-        <v>9.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05118560791015625</v>
+        <v>0.2423415184020996</v>
       </c>
       <c r="G52" t="n">
-        <v>1.352430105209351</v>
+        <v>11.92773461341858</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1798,13 +1798,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.8527312278747559</v>
+        <v>27.76166749000549</v>
       </c>
       <c r="B53" t="n">
-        <v>1437.03125</v>
+        <v>1444.12890625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.800000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.04849863052368164</v>
+        <v>0.2384963035583496</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8042299747467041</v>
+        <v>27.52316856384277</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1824,13 +1824,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.4154658317565918</v>
+        <v>13.72128939628601</v>
       </c>
       <c r="B54" t="n">
-        <v>1437.0625</v>
+        <v>1444.18359375</v>
       </c>
       <c r="C54" t="n">
-        <v>9.199999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04831838607788086</v>
+        <v>0.243248462677002</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3671443462371826</v>
+        <v>13.47803831100464</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.9744696617126465</v>
+        <v>11.77563858032227</v>
       </c>
       <c r="B55" t="n">
-        <v>1437.15234375</v>
+        <v>1444.18359375</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>14.2</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05098199844360352</v>
+        <v>0.2531633377075195</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9234855175018311</v>
+        <v>11.52247285842896</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.484592914581299</v>
+        <v>4125.721278429031</v>
       </c>
       <c r="B56" t="n">
-        <v>1437.15234375</v>
+        <v>1449.90625</v>
       </c>
       <c r="C56" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05294489860534668</v>
+        <v>0.2388730049133301</v>
       </c>
       <c r="G56" t="n">
-        <v>1.43164587020874</v>
+        <v>4125.482402801514</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.104376792907715</v>
+        <v>47.87333703041077</v>
       </c>
       <c r="B57" t="n">
-        <v>1437.171875</v>
+        <v>1449.90625</v>
       </c>
       <c r="C57" t="n">
-        <v>9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1917,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.05675482749938965</v>
+        <v>1.301597833633423</v>
       </c>
       <c r="G57" t="n">
-        <v>1.047619342803955</v>
+        <v>46.57173633575439</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.4971168041229248</v>
+        <v>32.5991153717041</v>
       </c>
       <c r="B58" t="n">
-        <v>1437.171875</v>
+        <v>1449.90625</v>
       </c>
       <c r="C58" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05186247825622559</v>
+        <v>0.2399046421051025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4452519416809082</v>
+        <v>32.35920858383179</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1954,13 +1954,13 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.9193322658538818</v>
+        <v>21.63844180107117</v>
       </c>
       <c r="B59" t="n">
-        <v>1437.19140625</v>
+        <v>1449.90625</v>
       </c>
       <c r="C59" t="n">
-        <v>18.2</v>
+        <v>13.7</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04835367202758789</v>
+        <v>0.2755162715911865</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8709759712219238</v>
+        <v>21.36292290687561</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.6531040668487549</v>
+        <v>52.88502764701843</v>
       </c>
       <c r="B60" t="n">
-        <v>1437.1953125</v>
+        <v>1449.90625</v>
       </c>
       <c r="C60" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.05022883415222168</v>
+        <v>0.2716195583343506</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6028733253479004</v>
+        <v>52.61340546607971</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2006,13 +2006,13 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2.156737327575684</v>
+        <v>26.06328940391541</v>
       </c>
       <c r="B61" t="n">
-        <v>1437.2109375</v>
+        <v>1449.90625</v>
       </c>
       <c r="C61" t="n">
-        <v>13.4</v>
+        <v>14.7</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2021,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05083203315734863</v>
+        <v>0.2403631210327148</v>
       </c>
       <c r="G61" t="n">
-        <v>2.105902910232544</v>
+        <v>25.82292413711548</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2032,13 +2032,13 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.62215256690979</v>
+        <v>12.90255641937256</v>
       </c>
       <c r="B62" t="n">
-        <v>1437.21484375</v>
+        <v>1449.90625</v>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0482642650604248</v>
+        <v>0.2366228103637695</v>
       </c>
       <c r="G62" t="n">
-        <v>1.573885679244995</v>
+        <v>12.66593050956726</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.889605045318604</v>
+        <v>17.4331750869751</v>
       </c>
       <c r="B63" t="n">
-        <v>1437.28515625</v>
+        <v>1449.90625</v>
       </c>
       <c r="C63" t="n">
-        <v>9.5</v>
+        <v>14.7</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2073,10 +2073,10 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04846763610839844</v>
+        <v>0.2767863273620605</v>
       </c>
       <c r="G63" t="n">
-        <v>1.841134786605835</v>
+        <v>17.1563868522644</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2084,13 +2084,13 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.396763563156128</v>
+        <v>20.41695928573608</v>
       </c>
       <c r="B64" t="n">
-        <v>1437.37109375</v>
+        <v>1449.90625</v>
       </c>
       <c r="C64" t="n">
-        <v>8.9</v>
+        <v>13.6</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2099,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04960274696350098</v>
+        <v>0.2439033985137939</v>
       </c>
       <c r="G64" t="n">
-        <v>1.347158193588257</v>
+        <v>20.17305374145508</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.178769111633301</v>
+        <v>7.869426727294922</v>
       </c>
       <c r="B65" t="n">
-        <v>1437.37109375</v>
+        <v>1449.90625</v>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0506138801574707</v>
+        <v>0.2371289730072021</v>
       </c>
       <c r="G65" t="n">
-        <v>1.128152370452881</v>
+        <v>7.632293224334717</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2136,13 +2136,13 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.558030128479004</v>
+        <v>12.87119054794312</v>
       </c>
       <c r="B66" t="n">
-        <v>1437.46875</v>
+        <v>1449.90625</v>
       </c>
       <c r="C66" t="n">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.05485844612121582</v>
+        <v>0.4214663505554199</v>
       </c>
       <c r="G66" t="n">
-        <v>1.503169298171997</v>
+        <v>12.44972133636475</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2162,13 +2162,13 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>393.8291125297546</v>
+        <v>9.633788108825684</v>
       </c>
       <c r="B67" t="n">
-        <v>1438.1328125</v>
+        <v>1449.90625</v>
       </c>
       <c r="C67" t="n">
-        <v>11.2</v>
+        <v>14.2</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04901838302612305</v>
+        <v>0.2804958820343018</v>
       </c>
       <c r="G67" t="n">
-        <v>393.7800920009613</v>
+        <v>9.353290319442749</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2188,13 +2188,13 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3.380919456481934</v>
+        <v>26.1925208568573</v>
       </c>
       <c r="B68" t="n">
-        <v>1438.13671875</v>
+        <v>1449.90625</v>
       </c>
       <c r="C68" t="n">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3026533126831055</v>
+        <v>0.2756891250610352</v>
       </c>
       <c r="G68" t="n">
-        <v>3.0782630443573</v>
+        <v>25.91682982444763</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
